--- a/verification/report-samples/office.xlsx
+++ b/verification/report-samples/office.xlsx
@@ -7,7 +7,7 @@
     <sheet sheetId="1" name="Report" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A1:$CF14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A1:$CF18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$8</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
   <si>
     <t>Gujjar Brother Transport — TEST DATA ONLY</t>
   </si>
@@ -26,7 +26,7 @@
     <t>OFFICE -TEST accounting period</t>
   </si>
   <si>
-    <t>2026-01-01 to 2026-12-31 · PKR · 2026-10-06T19:37:01.34+00:00</t>
+    <t>2026-01-01 to 2026-12-31 · PKR · 2026-10-11T16:34:22.165+00:00</t>
   </si>
   <si>
     <t>INCOMPLETE — missing mappings/sources; review notes.</t>
@@ -38,31 +38,31 @@
     <t>Date</t>
   </si>
   <si>
-    <t>Vehical</t>
-  </si>
-  <si>
-    <t>driver</t>
-  </si>
-  <si>
-    <t>Mobile-no</t>
-  </si>
-  <si>
-    <t>Things</t>
-  </si>
-  <si>
-    <t>From</t>
-  </si>
-  <si>
-    <t>Where</t>
-  </si>
-  <si>
-    <t>Rent/U/N</t>
-  </si>
-  <si>
-    <t>com</t>
-  </si>
-  <si>
-    <t>total</t>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>Contact number</t>
+  </si>
+  <si>
+    <t>Cargo</t>
+  </si>
+  <si>
+    <t>Origin</t>
+  </si>
+  <si>
+    <t>Destination</t>
+  </si>
+  <si>
+    <t>Freight</t>
+  </si>
+  <si>
+    <t>Commission</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
   <si>
     <t>Expense</t>
@@ -96,6 +96,17 @@
   </si>
   <si>
     <t>PERIOD TOTAL</t>
+  </si>
+  <si>
+    <t>Prepared by</t>
+  </si>
+  <si>
+    <t>Authorized officer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature: __________________
+Name: ____________________
+Date: _____________________</t>
   </si>
   <si>
     <t>com = approved brokerage commission; total = daily commission; Bill = unallocated approved office expenses once per day; P/L = total − Bill. Quoted freight is not recognized brokerage revenue.</t>
@@ -606,7 +617,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CF14"/>
+  <dimension ref="A1:CF18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="84" width="1.35" customWidth="1"/>
@@ -1156,72 +1167,72 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="3" t="s">
+      <c r="L8" s="3"/>
+      <c r="M8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
-      <c r="R8" s="3" t="s">
+      <c r="R8" s="3"/>
+      <c r="S8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="S8" s="3"/>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
-      <c r="W8" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
+      <c r="Z8" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
-      <c r="AC8" s="3" t="s">
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AD8" s="3"/>
-      <c r="AE8" s="3"/>
       <c r="AF8" s="3"/>
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
-      <c r="AI8" s="3" t="s">
+      <c r="AI8" s="3"/>
+      <c r="AJ8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AJ8" s="3"/>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
       <c r="AM8" s="3"/>
-      <c r="AN8" s="3" t="s">
+      <c r="AN8" s="3"/>
+      <c r="AO8" s="3"/>
+      <c r="AP8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="AO8" s="3"/>
-      <c r="AP8" s="3"/>
       <c r="AQ8" s="3"/>
       <c r="AR8" s="3"/>
       <c r="AS8" s="3"/>
-      <c r="AT8" s="3" t="s">
+      <c r="AT8" s="3"/>
+      <c r="AU8" s="3"/>
+      <c r="AV8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="AU8" s="3"/>
-      <c r="AV8" s="3"/>
       <c r="AW8" s="3"/>
       <c r="AX8" s="3"/>
-      <c r="AY8" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="AY8" s="3"/>
       <c r="AZ8" s="3"/>
       <c r="BA8" s="3"/>
-      <c r="BB8" s="3"/>
+      <c r="BB8" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="BC8" s="3"/>
       <c r="BD8" s="3"/>
-      <c r="BE8" s="3" t="s">
+      <c r="BE8" s="3"/>
+      <c r="BF8" s="3"/>
+      <c r="BG8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="BF8" s="3"/>
-      <c r="BG8" s="3"/>
       <c r="BH8" s="3"/>
       <c r="BI8" s="3"/>
       <c r="BJ8" s="3"/>
@@ -1236,17 +1247,17 @@
       <c r="BS8" s="3"/>
       <c r="BT8" s="3"/>
       <c r="BU8" s="3"/>
-      <c r="BV8" s="3" t="s">
+      <c r="BV8" s="3"/>
+      <c r="BW8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="BW8" s="3"/>
       <c r="BX8" s="3"/>
       <c r="BY8" s="3"/>
       <c r="BZ8" s="3"/>
-      <c r="CA8" s="3" t="s">
+      <c r="CA8" s="3"/>
+      <c r="CB8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="CB8" s="3"/>
       <c r="CC8" s="3"/>
       <c r="CD8" s="3"/>
       <c r="CE8" s="3"/>
@@ -1254,7 +1265,7 @@
     </row>
     <row r="9" ht="26" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>46302</v>
+        <v>46306</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1274,64 +1285,64 @@
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
-      <c r="R9" s="6" t="s">
+      <c r="R9" s="6"/>
+      <c r="S9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="S9" s="6"/>
       <c r="T9" s="6"/>
       <c r="U9" s="6"/>
       <c r="V9" s="6"/>
-      <c r="W9" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="W9" s="6"/>
       <c r="X9" s="6"/>
       <c r="Y9" s="6"/>
-      <c r="Z9" s="6"/>
+      <c r="Z9" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="AA9" s="6"/>
       <c r="AB9" s="6"/>
-      <c r="AC9" s="6" t="s">
+      <c r="AC9" s="6"/>
+      <c r="AD9" s="6"/>
+      <c r="AE9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="AD9" s="6"/>
-      <c r="AE9" s="6"/>
       <c r="AF9" s="6"/>
       <c r="AG9" s="6"/>
       <c r="AH9" s="6"/>
-      <c r="AI9" s="6" t="s">
+      <c r="AI9" s="6"/>
+      <c r="AJ9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="AJ9" s="6"/>
       <c r="AK9" s="6"/>
       <c r="AL9" s="6"/>
       <c r="AM9" s="6"/>
-      <c r="AN9" s="7">
+      <c r="AN9" s="6"/>
+      <c r="AO9" s="6"/>
+      <c r="AP9" s="7">
         <v>45000</v>
       </c>
-      <c r="AO9" s="7"/>
-      <c r="AP9" s="7"/>
       <c r="AQ9" s="7"/>
       <c r="AR9" s="7"/>
       <c r="AS9" s="7"/>
-      <c r="AT9" s="7">
+      <c r="AT9" s="7"/>
+      <c r="AU9" s="7"/>
+      <c r="AV9" s="7">
         <v>1500</v>
       </c>
-      <c r="AU9" s="7"/>
-      <c r="AV9" s="7"/>
       <c r="AW9" s="7"/>
       <c r="AX9" s="7"/>
-      <c r="AY9" s="7">
-        <v>3000</v>
-      </c>
+      <c r="AY9" s="7"/>
       <c r="AZ9" s="7"/>
       <c r="BA9" s="7"/>
-      <c r="BB9" s="7"/>
+      <c r="BB9" s="7">
+        <v>3000</v>
+      </c>
       <c r="BC9" s="7"/>
       <c r="BD9" s="7"/>
-      <c r="BE9" s="6" t="s">
+      <c r="BE9" s="7"/>
+      <c r="BF9" s="7"/>
+      <c r="BG9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="BF9" s="6"/>
-      <c r="BG9" s="6"/>
       <c r="BH9" s="6"/>
       <c r="BI9" s="6"/>
       <c r="BJ9" s="6"/>
@@ -1346,17 +1357,17 @@
       <c r="BS9" s="6"/>
       <c r="BT9" s="6"/>
       <c r="BU9" s="6"/>
-      <c r="BV9" s="7">
+      <c r="BV9" s="6"/>
+      <c r="BW9" s="7">
         <v>400</v>
       </c>
-      <c r="BW9" s="7"/>
       <c r="BX9" s="7"/>
       <c r="BY9" s="7"/>
       <c r="BZ9" s="7"/>
-      <c r="CA9" s="7">
+      <c r="CA9" s="7"/>
+      <c r="CB9" s="7">
         <v>2600</v>
       </c>
-      <c r="CB9" s="7"/>
       <c r="CC9" s="7"/>
       <c r="CD9" s="7"/>
       <c r="CE9" s="7"/>
@@ -1382,49 +1393,49 @@
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
-      <c r="R10" s="6" t="s">
+      <c r="R10" s="6"/>
+      <c r="S10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="S10" s="6"/>
       <c r="T10" s="6"/>
       <c r="U10" s="6"/>
       <c r="V10" s="6"/>
-      <c r="W10" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="W10" s="6"/>
       <c r="X10" s="6"/>
       <c r="Y10" s="6"/>
-      <c r="Z10" s="6"/>
+      <c r="Z10" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="AA10" s="6"/>
       <c r="AB10" s="6"/>
-      <c r="AC10" s="6" t="s">
+      <c r="AC10" s="6"/>
+      <c r="AD10" s="6"/>
+      <c r="AE10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="AD10" s="6"/>
-      <c r="AE10" s="6"/>
       <c r="AF10" s="6"/>
       <c r="AG10" s="6"/>
       <c r="AH10" s="6"/>
-      <c r="AI10" s="6" t="s">
+      <c r="AI10" s="6"/>
+      <c r="AJ10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="AJ10" s="6"/>
       <c r="AK10" s="6"/>
       <c r="AL10" s="6"/>
       <c r="AM10" s="6"/>
-      <c r="AN10" s="7">
+      <c r="AN10" s="6"/>
+      <c r="AO10" s="6"/>
+      <c r="AP10" s="7">
         <v>45000</v>
       </c>
-      <c r="AO10" s="7"/>
-      <c r="AP10" s="7"/>
       <c r="AQ10" s="7"/>
       <c r="AR10" s="7"/>
       <c r="AS10" s="7"/>
-      <c r="AT10" s="7">
+      <c r="AT10" s="7"/>
+      <c r="AU10" s="7"/>
+      <c r="AV10" s="7">
         <v>1500</v>
       </c>
-      <c r="AU10" s="7"/>
-      <c r="AV10" s="7"/>
       <c r="AW10" s="7"/>
       <c r="AX10" s="7"/>
       <c r="AY10" s="7"/>
@@ -1433,8 +1444,8 @@
       <c r="BB10" s="7"/>
       <c r="BC10" s="7"/>
       <c r="BD10" s="7"/>
-      <c r="BE10" s="6"/>
-      <c r="BF10" s="6"/>
+      <c r="BE10" s="7"/>
+      <c r="BF10" s="7"/>
       <c r="BG10" s="6"/>
       <c r="BH10" s="6"/>
       <c r="BI10" s="6"/>
@@ -1450,7 +1461,7 @@
       <c r="BS10" s="6"/>
       <c r="BT10" s="6"/>
       <c r="BU10" s="6"/>
-      <c r="BV10" s="7"/>
+      <c r="BV10" s="6"/>
       <c r="BW10" s="7"/>
       <c r="BX10" s="7"/>
       <c r="BY10" s="7"/>
@@ -1504,29 +1515,29 @@
       <c r="AK11" s="9"/>
       <c r="AL11" s="9"/>
       <c r="AM11" s="9"/>
-      <c r="AN11" s="10"/>
-      <c r="AO11" s="10"/>
+      <c r="AN11" s="9"/>
+      <c r="AO11" s="9"/>
       <c r="AP11" s="10"/>
       <c r="AQ11" s="10"/>
       <c r="AR11" s="10"/>
       <c r="AS11" s="10"/>
-      <c r="AT11" s="10">
+      <c r="AT11" s="10"/>
+      <c r="AU11" s="10"/>
+      <c r="AV11" s="10">
         <v>3000</v>
       </c>
-      <c r="AU11" s="10"/>
-      <c r="AV11" s="10"/>
       <c r="AW11" s="10"/>
       <c r="AX11" s="10"/>
-      <c r="AY11" s="10">
-        <v>3000</v>
-      </c>
+      <c r="AY11" s="10"/>
       <c r="AZ11" s="10"/>
       <c r="BA11" s="10"/>
-      <c r="BB11" s="10"/>
+      <c r="BB11" s="10">
+        <v>3000</v>
+      </c>
       <c r="BC11" s="10"/>
       <c r="BD11" s="10"/>
-      <c r="BE11" s="9"/>
-      <c r="BF11" s="9"/>
+      <c r="BE11" s="10"/>
+      <c r="BF11" s="10"/>
       <c r="BG11" s="9"/>
       <c r="BH11" s="9"/>
       <c r="BI11" s="9"/>
@@ -1542,200 +1553,468 @@
       <c r="BS11" s="9"/>
       <c r="BT11" s="9"/>
       <c r="BU11" s="9"/>
-      <c r="BV11" s="10">
+      <c r="BV11" s="9"/>
+      <c r="BW11" s="10">
         <v>400</v>
       </c>
-      <c r="BW11" s="10"/>
       <c r="BX11" s="10"/>
       <c r="BY11" s="10"/>
       <c r="BZ11" s="10"/>
-      <c r="CA11" s="10">
+      <c r="CA11" s="10"/>
+      <c r="CB11" s="10">
         <v>2600</v>
       </c>
-      <c r="CB11" s="10"/>
       <c r="CC11" s="10"/>
       <c r="CD11" s="10"/>
       <c r="CE11" s="10"/>
       <c r="CF11" s="10"/>
     </row>
-    <row r="13" ht="30" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="13" ht="22" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="3"/>
+      <c r="AC13" s="3"/>
+      <c r="AD13" s="3"/>
+      <c r="AE13" s="3"/>
+      <c r="AF13" s="3"/>
+      <c r="AG13" s="3"/>
+      <c r="AH13" s="3"/>
+      <c r="AI13" s="3"/>
+      <c r="AJ13" s="3"/>
+      <c r="AK13" s="3"/>
+      <c r="AL13" s="3"/>
+      <c r="AM13" s="3"/>
+      <c r="AN13" s="3"/>
+      <c r="AO13" s="3"/>
+      <c r="AP13" s="3"/>
+      <c r="AQ13" s="3"/>
+      <c r="AR13" s="3"/>
+      <c r="AS13" s="3"/>
+      <c r="AT13" s="3"/>
+      <c r="AU13" s="3"/>
+      <c r="AV13" s="3"/>
+      <c r="AW13" s="3"/>
+      <c r="AX13" s="3"/>
+      <c r="AY13" s="3"/>
+      <c r="AZ13" s="3"/>
+      <c r="BA13" s="3"/>
+      <c r="BB13" s="3"/>
+      <c r="BC13" s="3"/>
+      <c r="BD13" s="3"/>
+      <c r="BE13" s="3"/>
+      <c r="BF13" s="3"/>
+      <c r="BG13" s="3"/>
+      <c r="BH13" s="3"/>
+      <c r="BI13" s="3"/>
+      <c r="BJ13" s="3"/>
+      <c r="BK13" s="3"/>
+      <c r="BL13" s="3"/>
+      <c r="BM13" s="3"/>
+      <c r="BN13" s="3"/>
+      <c r="BO13" s="3"/>
+      <c r="BP13" s="3"/>
+      <c r="BQ13" s="3"/>
+      <c r="BR13" s="3"/>
+      <c r="BS13" s="3"/>
+      <c r="BT13" s="3"/>
+      <c r="BU13" s="3"/>
+      <c r="BV13" s="3"/>
+      <c r="BW13" s="3"/>
+      <c r="BX13" s="3"/>
+      <c r="BY13" s="3"/>
+      <c r="BZ13" s="3"/>
+      <c r="CA13" s="3"/>
+      <c r="CB13" s="3"/>
+      <c r="CC13" s="3"/>
+      <c r="CD13" s="3"/>
+      <c r="CE13" s="3"/>
+      <c r="CF13" s="3"/>
+    </row>
+    <row r="14" ht="45" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-      <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
-      <c r="X13" s="2"/>
-      <c r="Y13" s="2"/>
-      <c r="Z13" s="2"/>
-      <c r="AA13" s="2"/>
-      <c r="AB13" s="2"/>
-      <c r="AC13" s="2"/>
-      <c r="AD13" s="2"/>
-      <c r="AE13" s="2"/>
-      <c r="AF13" s="2"/>
-      <c r="AG13" s="2"/>
-      <c r="AH13" s="2"/>
-      <c r="AI13" s="2"/>
-      <c r="AJ13" s="2"/>
-      <c r="AK13" s="2"/>
-      <c r="AL13" s="2"/>
-      <c r="AM13" s="2"/>
-      <c r="AN13" s="2"/>
-      <c r="AO13" s="2"/>
-      <c r="AP13" s="2"/>
-      <c r="AQ13" s="2"/>
-      <c r="AR13" s="2"/>
-      <c r="AS13" s="2"/>
-      <c r="AT13" s="2"/>
-      <c r="AU13" s="2"/>
-      <c r="AV13" s="2"/>
-      <c r="AW13" s="2"/>
-      <c r="AX13" s="2"/>
-      <c r="AY13" s="2"/>
-      <c r="AZ13" s="2"/>
-      <c r="BA13" s="2"/>
-      <c r="BB13" s="2"/>
-      <c r="BC13" s="2"/>
-      <c r="BD13" s="2"/>
-      <c r="BE13" s="2"/>
-      <c r="BF13" s="2"/>
-      <c r="BG13" s="2"/>
-      <c r="BH13" s="2"/>
-      <c r="BI13" s="2"/>
-      <c r="BJ13" s="2"/>
-      <c r="BK13" s="2"/>
-      <c r="BL13" s="2"/>
-      <c r="BM13" s="2"/>
-      <c r="BN13" s="2"/>
-      <c r="BO13" s="2"/>
-      <c r="BP13" s="2"/>
-      <c r="BQ13" s="2"/>
-      <c r="BR13" s="2"/>
-      <c r="BS13" s="2"/>
-      <c r="BT13" s="2"/>
-      <c r="BU13" s="2"/>
-      <c r="BV13" s="2"/>
-      <c r="BW13" s="2"/>
-      <c r="BX13" s="2"/>
-      <c r="BY13" s="2"/>
-      <c r="BZ13" s="2"/>
-      <c r="CA13" s="2"/>
-      <c r="CB13" s="2"/>
-      <c r="CC13" s="2"/>
-      <c r="CD13" s="2"/>
-      <c r="CE13" s="2"/>
-      <c r="CF13" s="2"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3"/>
+      <c r="X14" s="3"/>
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="3"/>
+      <c r="AC14" s="3"/>
+      <c r="AD14" s="3"/>
+      <c r="AE14" s="3"/>
+      <c r="AF14" s="3"/>
+      <c r="AG14" s="3"/>
+      <c r="AH14" s="3"/>
+      <c r="AI14" s="3"/>
+      <c r="AJ14" s="3"/>
+      <c r="AK14" s="3"/>
+      <c r="AL14" s="3"/>
+      <c r="AM14" s="3"/>
+      <c r="AN14" s="3"/>
+      <c r="AO14" s="3"/>
+      <c r="AP14" s="3"/>
+      <c r="AQ14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AR14" s="3"/>
+      <c r="AS14" s="3"/>
+      <c r="AT14" s="3"/>
+      <c r="AU14" s="3"/>
+      <c r="AV14" s="3"/>
+      <c r="AW14" s="3"/>
+      <c r="AX14" s="3"/>
+      <c r="AY14" s="3"/>
+      <c r="AZ14" s="3"/>
+      <c r="BA14" s="3"/>
+      <c r="BB14" s="3"/>
+      <c r="BC14" s="3"/>
+      <c r="BD14" s="3"/>
+      <c r="BE14" s="3"/>
+      <c r="BF14" s="3"/>
+      <c r="BG14" s="3"/>
+      <c r="BH14" s="3"/>
+      <c r="BI14" s="3"/>
+      <c r="BJ14" s="3"/>
+      <c r="BK14" s="3"/>
+      <c r="BL14" s="3"/>
+      <c r="BM14" s="3"/>
+      <c r="BN14" s="3"/>
+      <c r="BO14" s="3"/>
+      <c r="BP14" s="3"/>
+      <c r="BQ14" s="3"/>
+      <c r="BR14" s="3"/>
+      <c r="BS14" s="3"/>
+      <c r="BT14" s="3"/>
+      <c r="BU14" s="3"/>
+      <c r="BV14" s="3"/>
+      <c r="BW14" s="3"/>
+      <c r="BX14" s="3"/>
+      <c r="BY14" s="3"/>
+      <c r="BZ14" s="3"/>
+      <c r="CA14" s="3"/>
+      <c r="CB14" s="3"/>
+      <c r="CC14" s="3"/>
+      <c r="CD14" s="3"/>
+      <c r="CE14" s="3"/>
+      <c r="CF14" s="3"/>
     </row>
-    <row r="14" ht="30" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
-      <c r="Y14" s="2"/>
-      <c r="Z14" s="2"/>
-      <c r="AA14" s="2"/>
-      <c r="AB14" s="2"/>
-      <c r="AC14" s="2"/>
-      <c r="AD14" s="2"/>
-      <c r="AE14" s="2"/>
-      <c r="AF14" s="2"/>
-      <c r="AG14" s="2"/>
-      <c r="AH14" s="2"/>
-      <c r="AI14" s="2"/>
-      <c r="AJ14" s="2"/>
-      <c r="AK14" s="2"/>
-      <c r="AL14" s="2"/>
-      <c r="AM14" s="2"/>
-      <c r="AN14" s="2"/>
-      <c r="AO14" s="2"/>
-      <c r="AP14" s="2"/>
-      <c r="AQ14" s="2"/>
-      <c r="AR14" s="2"/>
-      <c r="AS14" s="2"/>
-      <c r="AT14" s="2"/>
-      <c r="AU14" s="2"/>
-      <c r="AV14" s="2"/>
-      <c r="AW14" s="2"/>
-      <c r="AX14" s="2"/>
-      <c r="AY14" s="2"/>
-      <c r="AZ14" s="2"/>
-      <c r="BA14" s="2"/>
-      <c r="BB14" s="2"/>
-      <c r="BC14" s="2"/>
-      <c r="BD14" s="2"/>
-      <c r="BE14" s="2"/>
-      <c r="BF14" s="2"/>
-      <c r="BG14" s="2"/>
-      <c r="BH14" s="2"/>
-      <c r="BI14" s="2"/>
-      <c r="BJ14" s="2"/>
-      <c r="BK14" s="2"/>
-      <c r="BL14" s="2"/>
-      <c r="BM14" s="2"/>
-      <c r="BN14" s="2"/>
-      <c r="BO14" s="2"/>
-      <c r="BP14" s="2"/>
-      <c r="BQ14" s="2"/>
-      <c r="BR14" s="2"/>
-      <c r="BS14" s="2"/>
-      <c r="BT14" s="2"/>
-      <c r="BU14" s="2"/>
-      <c r="BV14" s="2"/>
-      <c r="BW14" s="2"/>
-      <c r="BX14" s="2"/>
-      <c r="BY14" s="2"/>
-      <c r="BZ14" s="2"/>
-      <c r="CA14" s="2"/>
-      <c r="CB14" s="2"/>
-      <c r="CC14" s="2"/>
-      <c r="CD14" s="2"/>
-      <c r="CE14" s="2"/>
-      <c r="CF14" s="2"/>
+    <row r="15" ht="85" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="6"/>
+      <c r="Y15" s="6"/>
+      <c r="Z15" s="6"/>
+      <c r="AA15" s="6"/>
+      <c r="AB15" s="6"/>
+      <c r="AC15" s="6"/>
+      <c r="AD15" s="6"/>
+      <c r="AE15" s="6"/>
+      <c r="AF15" s="6"/>
+      <c r="AG15" s="6"/>
+      <c r="AH15" s="6"/>
+      <c r="AI15" s="6"/>
+      <c r="AJ15" s="6"/>
+      <c r="AK15" s="6"/>
+      <c r="AL15" s="6"/>
+      <c r="AM15" s="6"/>
+      <c r="AN15" s="6"/>
+      <c r="AO15" s="6"/>
+      <c r="AP15" s="6"/>
+      <c r="AQ15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="AR15" s="6"/>
+      <c r="AS15" s="6"/>
+      <c r="AT15" s="6"/>
+      <c r="AU15" s="6"/>
+      <c r="AV15" s="6"/>
+      <c r="AW15" s="6"/>
+      <c r="AX15" s="6"/>
+      <c r="AY15" s="6"/>
+      <c r="AZ15" s="6"/>
+      <c r="BA15" s="6"/>
+      <c r="BB15" s="6"/>
+      <c r="BC15" s="6"/>
+      <c r="BD15" s="6"/>
+      <c r="BE15" s="6"/>
+      <c r="BF15" s="6"/>
+      <c r="BG15" s="6"/>
+      <c r="BH15" s="6"/>
+      <c r="BI15" s="6"/>
+      <c r="BJ15" s="6"/>
+      <c r="BK15" s="6"/>
+      <c r="BL15" s="6"/>
+      <c r="BM15" s="6"/>
+      <c r="BN15" s="6"/>
+      <c r="BO15" s="6"/>
+      <c r="BP15" s="6"/>
+      <c r="BQ15" s="6"/>
+      <c r="BR15" s="6"/>
+      <c r="BS15" s="6"/>
+      <c r="BT15" s="6"/>
+      <c r="BU15" s="6"/>
+      <c r="BV15" s="6"/>
+      <c r="BW15" s="6"/>
+      <c r="BX15" s="6"/>
+      <c r="BY15" s="6"/>
+      <c r="BZ15" s="6"/>
+      <c r="CA15" s="6"/>
+      <c r="CB15" s="6"/>
+      <c r="CC15" s="6"/>
+      <c r="CD15" s="6"/>
+      <c r="CE15" s="6"/>
+      <c r="CF15" s="6"/>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
+      <c r="Z17" s="2"/>
+      <c r="AA17" s="2"/>
+      <c r="AB17" s="2"/>
+      <c r="AC17" s="2"/>
+      <c r="AD17" s="2"/>
+      <c r="AE17" s="2"/>
+      <c r="AF17" s="2"/>
+      <c r="AG17" s="2"/>
+      <c r="AH17" s="2"/>
+      <c r="AI17" s="2"/>
+      <c r="AJ17" s="2"/>
+      <c r="AK17" s="2"/>
+      <c r="AL17" s="2"/>
+      <c r="AM17" s="2"/>
+      <c r="AN17" s="2"/>
+      <c r="AO17" s="2"/>
+      <c r="AP17" s="2"/>
+      <c r="AQ17" s="2"/>
+      <c r="AR17" s="2"/>
+      <c r="AS17" s="2"/>
+      <c r="AT17" s="2"/>
+      <c r="AU17" s="2"/>
+      <c r="AV17" s="2"/>
+      <c r="AW17" s="2"/>
+      <c r="AX17" s="2"/>
+      <c r="AY17" s="2"/>
+      <c r="AZ17" s="2"/>
+      <c r="BA17" s="2"/>
+      <c r="BB17" s="2"/>
+      <c r="BC17" s="2"/>
+      <c r="BD17" s="2"/>
+      <c r="BE17" s="2"/>
+      <c r="BF17" s="2"/>
+      <c r="BG17" s="2"/>
+      <c r="BH17" s="2"/>
+      <c r="BI17" s="2"/>
+      <c r="BJ17" s="2"/>
+      <c r="BK17" s="2"/>
+      <c r="BL17" s="2"/>
+      <c r="BM17" s="2"/>
+      <c r="BN17" s="2"/>
+      <c r="BO17" s="2"/>
+      <c r="BP17" s="2"/>
+      <c r="BQ17" s="2"/>
+      <c r="BR17" s="2"/>
+      <c r="BS17" s="2"/>
+      <c r="BT17" s="2"/>
+      <c r="BU17" s="2"/>
+      <c r="BV17" s="2"/>
+      <c r="BW17" s="2"/>
+      <c r="BX17" s="2"/>
+      <c r="BY17" s="2"/>
+      <c r="BZ17" s="2"/>
+      <c r="CA17" s="2"/>
+      <c r="CB17" s="2"/>
+      <c r="CC17" s="2"/>
+      <c r="CD17" s="2"/>
+      <c r="CE17" s="2"/>
+      <c r="CF17" s="2"/>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
+      <c r="Z18" s="2"/>
+      <c r="AA18" s="2"/>
+      <c r="AB18" s="2"/>
+      <c r="AC18" s="2"/>
+      <c r="AD18" s="2"/>
+      <c r="AE18" s="2"/>
+      <c r="AF18" s="2"/>
+      <c r="AG18" s="2"/>
+      <c r="AH18" s="2"/>
+      <c r="AI18" s="2"/>
+      <c r="AJ18" s="2"/>
+      <c r="AK18" s="2"/>
+      <c r="AL18" s="2"/>
+      <c r="AM18" s="2"/>
+      <c r="AN18" s="2"/>
+      <c r="AO18" s="2"/>
+      <c r="AP18" s="2"/>
+      <c r="AQ18" s="2"/>
+      <c r="AR18" s="2"/>
+      <c r="AS18" s="2"/>
+      <c r="AT18" s="2"/>
+      <c r="AU18" s="2"/>
+      <c r="AV18" s="2"/>
+      <c r="AW18" s="2"/>
+      <c r="AX18" s="2"/>
+      <c r="AY18" s="2"/>
+      <c r="AZ18" s="2"/>
+      <c r="BA18" s="2"/>
+      <c r="BB18" s="2"/>
+      <c r="BC18" s="2"/>
+      <c r="BD18" s="2"/>
+      <c r="BE18" s="2"/>
+      <c r="BF18" s="2"/>
+      <c r="BG18" s="2"/>
+      <c r="BH18" s="2"/>
+      <c r="BI18" s="2"/>
+      <c r="BJ18" s="2"/>
+      <c r="BK18" s="2"/>
+      <c r="BL18" s="2"/>
+      <c r="BM18" s="2"/>
+      <c r="BN18" s="2"/>
+      <c r="BO18" s="2"/>
+      <c r="BP18" s="2"/>
+      <c r="BQ18" s="2"/>
+      <c r="BR18" s="2"/>
+      <c r="BS18" s="2"/>
+      <c r="BT18" s="2"/>
+      <c r="BU18" s="2"/>
+      <c r="BV18" s="2"/>
+      <c r="BW18" s="2"/>
+      <c r="BX18" s="2"/>
+      <c r="BY18" s="2"/>
+      <c r="BZ18" s="2"/>
+      <c r="CA18" s="2"/>
+      <c r="CB18" s="2"/>
+      <c r="CC18" s="2"/>
+      <c r="CD18" s="2"/>
+      <c r="CE18" s="2"/>
+      <c r="CF18" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="60">
     <mergeCell ref="A1:CF1"/>
     <mergeCell ref="A2:CF2"/>
     <mergeCell ref="A3:CF3"/>
@@ -1743,54 +2022,59 @@
     <mergeCell ref="A5:CF5"/>
     <mergeCell ref="A7:CF7"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="G8:K8"/>
-    <mergeCell ref="L8:Q8"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="W8:AB8"/>
-    <mergeCell ref="AC8:AH8"/>
-    <mergeCell ref="AI8:AM8"/>
-    <mergeCell ref="AN8:AS8"/>
-    <mergeCell ref="AT8:AX8"/>
-    <mergeCell ref="AY8:BD8"/>
-    <mergeCell ref="BE8:BU8"/>
-    <mergeCell ref="BV8:BZ8"/>
-    <mergeCell ref="CA8:CF8"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="M8:R8"/>
+    <mergeCell ref="S8:Y8"/>
+    <mergeCell ref="Z8:AD8"/>
+    <mergeCell ref="AE8:AI8"/>
+    <mergeCell ref="AJ8:AO8"/>
+    <mergeCell ref="AP8:AU8"/>
+    <mergeCell ref="AV8:BA8"/>
+    <mergeCell ref="BB8:BF8"/>
+    <mergeCell ref="BG8:BV8"/>
+    <mergeCell ref="BW8:CA8"/>
+    <mergeCell ref="CB8:CF8"/>
     <mergeCell ref="A9:F10"/>
-    <mergeCell ref="G9:K9"/>
-    <mergeCell ref="L9:Q9"/>
-    <mergeCell ref="R9:V9"/>
-    <mergeCell ref="W9:AB9"/>
-    <mergeCell ref="AC9:AH9"/>
-    <mergeCell ref="AI9:AM9"/>
-    <mergeCell ref="AN9:AS9"/>
-    <mergeCell ref="AT9:AX9"/>
-    <mergeCell ref="AY9:BD10"/>
-    <mergeCell ref="BE9:BU10"/>
-    <mergeCell ref="BV9:BZ10"/>
-    <mergeCell ref="CA9:CF10"/>
-    <mergeCell ref="G10:K10"/>
-    <mergeCell ref="L10:Q10"/>
-    <mergeCell ref="R10:V10"/>
-    <mergeCell ref="W10:AB10"/>
-    <mergeCell ref="AC10:AH10"/>
-    <mergeCell ref="AI10:AM10"/>
-    <mergeCell ref="AN10:AS10"/>
-    <mergeCell ref="AT10:AX10"/>
+    <mergeCell ref="G9:L9"/>
+    <mergeCell ref="M9:R9"/>
+    <mergeCell ref="S9:Y9"/>
+    <mergeCell ref="Z9:AD9"/>
+    <mergeCell ref="AE9:AI9"/>
+    <mergeCell ref="AJ9:AO9"/>
+    <mergeCell ref="AP9:AU9"/>
+    <mergeCell ref="AV9:BA9"/>
+    <mergeCell ref="BB9:BF10"/>
+    <mergeCell ref="BG9:BV10"/>
+    <mergeCell ref="BW9:CA10"/>
+    <mergeCell ref="CB9:CF10"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="M10:R10"/>
+    <mergeCell ref="S10:Y10"/>
+    <mergeCell ref="Z10:AD10"/>
+    <mergeCell ref="AE10:AI10"/>
+    <mergeCell ref="AJ10:AO10"/>
+    <mergeCell ref="AP10:AU10"/>
+    <mergeCell ref="AV10:BA10"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="L11:Q11"/>
-    <mergeCell ref="R11:V11"/>
-    <mergeCell ref="W11:AB11"/>
-    <mergeCell ref="AC11:AH11"/>
-    <mergeCell ref="AI11:AM11"/>
-    <mergeCell ref="AN11:AS11"/>
-    <mergeCell ref="AT11:AX11"/>
-    <mergeCell ref="AY11:BD11"/>
-    <mergeCell ref="BE11:BU11"/>
-    <mergeCell ref="BV11:BZ11"/>
-    <mergeCell ref="CA11:CF11"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="M11:R11"/>
+    <mergeCell ref="S11:Y11"/>
+    <mergeCell ref="Z11:AD11"/>
+    <mergeCell ref="AE11:AI11"/>
+    <mergeCell ref="AJ11:AO11"/>
+    <mergeCell ref="AP11:AU11"/>
+    <mergeCell ref="AV11:BA11"/>
+    <mergeCell ref="BB11:BF11"/>
+    <mergeCell ref="BG11:BV11"/>
+    <mergeCell ref="BW11:CA11"/>
+    <mergeCell ref="CB11:CF11"/>
     <mergeCell ref="A13:CF13"/>
-    <mergeCell ref="A14:CF14"/>
+    <mergeCell ref="A14:AP14"/>
+    <mergeCell ref="AQ14:CF14"/>
+    <mergeCell ref="A15:AP15"/>
+    <mergeCell ref="AQ15:CF15"/>
+    <mergeCell ref="A17:CF17"/>
+    <mergeCell ref="A18:CF18"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
